--- a/fixtures/dev/partners/partner-prep-synthetic.xlsx
+++ b/fixtures/dev/partners/partner-prep-synthetic.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>900000014</t>
+          <t>000000011</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Probna 1</t>
+          <t>PrimerulicaA 1</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -542,7 +542,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>900000022</t>
+          <t>000000020</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Probna 2</t>
+          <t>PrimerulicaA 2</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>900000039</t>
+          <t>000000038</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Probna 3</t>
+          <t>PrimerulicaA 3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>900000047</t>
+          <t>000000046</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -656,7 +656,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Probna 4</t>
+          <t>PrimerulicaA 4</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>900000055</t>
+          <t>000000054</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Probna 5</t>
+          <t>PrimerulicaA 5</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+381 11 555 0101</t>
+          <t>+381 60 555 0001</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>900000055</t>
+          <t>000000054</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Probna 6</t>
+          <t>PrimerulicaA 6</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Probna 7</t>
+          <t>PrimerulicaA 7</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>900000064</t>
+          <t>000000063</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -925,7 +925,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Probna 8</t>
+          <t>PrimerulicaA 8</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DE999999999</t>
+          <t>DE000000000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>900000071</t>
+          <t>000000087</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Probna 9</t>
+          <t>PrimerulicaA 9</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Probna</t>
+          <t>PrimerulicaA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>011/555-0101</t>
+          <t>060 555 0001</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Druga</t>
+          <t>PrimerulicaB</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+381600000000</t>
+          <t>+381 60 555 0002</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Treca</t>
+          <t>PrimerulicaC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+381600000001</t>
+          <t>+381 60 555 0003</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
